--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.50988102891745</v>
+        <v>4.307855667199086</v>
       </c>
       <c r="D2" t="n">
-        <v>26.41924654599526</v>
+        <v>4.29312756372423</v>
       </c>
       <c r="E2" t="n">
-        <v>5.649318272249107</v>
+        <v>0.91801421924048</v>
       </c>
       <c r="F2" t="n">
-        <v>5.738773840312072</v>
+        <v>0.9325507490507118</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.65213026626488</v>
+        <v>3.193471168268044</v>
       </c>
       <c r="D3" t="n">
-        <v>19.6273388435419</v>
+        <v>3.189442562075558</v>
       </c>
       <c r="E3" t="n">
-        <v>5.649318272249107</v>
+        <v>0.91801421924048</v>
       </c>
       <c r="F3" t="n">
-        <v>5.738773840312072</v>
+        <v>0.9325507490507118</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.08165368090902</v>
+        <v>5.538268723147716</v>
       </c>
       <c r="D4" t="n">
-        <v>34.30830564466046</v>
+        <v>5.575099667257325</v>
       </c>
       <c r="E4" t="n">
-        <v>5.649318272249107</v>
+        <v>0.91801421924048</v>
       </c>
       <c r="F4" t="n">
-        <v>5.738773840312072</v>
+        <v>0.9325507490507118</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.44012604433954</v>
+        <v>3.646520482205175</v>
       </c>
       <c r="D5" t="n">
-        <v>22.6506962541798</v>
+        <v>3.680738141304217</v>
       </c>
       <c r="E5" t="n">
-        <v>5.649318272249107</v>
+        <v>0.91801421924048</v>
       </c>
       <c r="F5" t="n">
-        <v>5.738773840312072</v>
+        <v>0.9325507490507118</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.62726402877105</v>
+        <v>4.489430404675296</v>
       </c>
       <c r="D6" t="n">
-        <v>27.73523951050708</v>
+        <v>4.5069764204574</v>
       </c>
       <c r="E6" t="n">
-        <v>5.649318272249107</v>
+        <v>0.91801421924048</v>
       </c>
       <c r="F6" t="n">
-        <v>5.738773840312072</v>
+        <v>0.9325507490507118</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.15481509928982</v>
+        <v>2.300157453634596</v>
       </c>
       <c r="D7" t="n">
-        <v>13.93236102392462</v>
+        <v>2.264008666387751</v>
       </c>
       <c r="E7" t="n">
-        <v>5.649318272249107</v>
+        <v>0.91801421924048</v>
       </c>
       <c r="F7" t="n">
-        <v>5.738773840312072</v>
+        <v>0.9325507490507118</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.14451179431424</v>
+        <v>4.573483166576064</v>
       </c>
       <c r="D8" t="n">
-        <v>27.91851518892226</v>
+        <v>4.536758718199868</v>
       </c>
       <c r="E8" t="n">
-        <v>5.649318272249107</v>
+        <v>0.91801421924048</v>
       </c>
       <c r="F8" t="n">
-        <v>5.738773840312072</v>
+        <v>0.9325507490507118</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.21768061479295</v>
+        <v>3.772873099903855</v>
       </c>
       <c r="D9" t="n">
-        <v>22.87949928442111</v>
+        <v>3.71791863371843</v>
       </c>
       <c r="E9" t="n">
-        <v>5.649318272249107</v>
+        <v>0.91801421924048</v>
       </c>
       <c r="F9" t="n">
-        <v>5.738773840312072</v>
+        <v>0.9325507490507118</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
